--- a/company/analytics/out/sample_集客売上_2026-10-16.xlsx
+++ b/company/analytics/out/sample_集客売上_2026-10-16.xlsx
@@ -113,90 +113,95 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">メルマガ配信数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">開封率</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">実質開封率</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">メルマガ読者</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">LINE追加</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">LINEブロック</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">LINE純増</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">LINE有効友だち</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">IGフォロワー</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">説明会申込</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">説明会参加</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">講座申込</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr" s="1">
+      <c r="O1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">入金額</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">個別相談</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">時間_講座</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
+      <c r="R1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">時間_発信</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="S1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">時間_事務</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr" s="1">
+      <c r="T1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">時間_配信代行</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr" s="1">
+      <c r="U1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">ワクワク度</t>
         </is>
@@ -211,46 +216,49 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
+        <v>238</v>
+      </c>
+      <c r="D2" s="2">
         <v>0.41416309012875535</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>0.46909999999999996</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>238</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>87</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>800</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>4</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>5</v>
       </c>
-      <c r="R2">
-        <v>2</v>
-      </c>
       <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
         <v>8</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>4</v>
       </c>
     </row>
@@ -263,18 +271,18 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
+        <v>238</v>
+      </c>
+      <c r="D3" s="2">
         <v>0.4172043010752688</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>0.46355</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>238</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -282,27 +290,30 @@
         <v>0</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>87</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>803</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>5</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>4</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>10</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>4</v>
       </c>
     </row>
@@ -315,46 +326,49 @@
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
+        <v>240</v>
+      </c>
+      <c r="D4" s="2">
         <v>0.425531914893617</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>0.47775000000000006</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>240</v>
       </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
         <v>89</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>806</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>1</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>4</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>5</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>4</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>6</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>4</v>
       </c>
     </row>
@@ -367,18 +381,18 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
+        <v>241</v>
+      </c>
+      <c r="D5" s="2">
         <v>0.42340425531914894</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>0.48275000000000007</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>241</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -386,24 +400,27 @@
         <v>0</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>89</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>1</v>
       </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>3</v>
       </c>
       <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
         <v>9</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>4</v>
       </c>
     </row>
@@ -416,18 +433,18 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
+        <v>242</v>
+      </c>
+      <c r="D6" s="2">
         <v>0.4194915254237288</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>0.46325000000000005</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>242</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -435,27 +452,30 @@
         <v>0</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>89</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>812</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>1</v>
       </c>
-      <c r="P6">
-        <v>2</v>
-      </c>
       <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
         <v>5</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>1</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>8</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>3</v>
       </c>
     </row>
@@ -468,51 +488,54 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
+        <v>242</v>
+      </c>
+      <c r="D7" s="2">
         <v>0.4240506329113924</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>0.48495000000000005</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>242</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
       <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>91</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>815</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>14</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>6</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>3</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>1</v>
-      </c>
-      <c r="S7">
-        <v>4</v>
       </c>
       <c r="T7">
         <v>4</v>
       </c>
+      <c r="U7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="1">
@@ -523,49 +546,52 @@
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
+        <v>244</v>
+      </c>
+      <c r="D8" s="2">
         <v>0.4126315789473684</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>0.4633</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>244</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
         <v>93</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>818</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>11</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>1</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>4</v>
       </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
       <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
         <v>1</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>5</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>3</v>
       </c>
     </row>
@@ -578,18 +604,18 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
+        <v>246</v>
+      </c>
+      <c r="D9" s="2">
         <v>0.42916666666666664</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>0.48265</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>246</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -597,24 +623,27 @@
         <v>0</v>
       </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>93</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>1</v>
       </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
       <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
         <v>5</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>3</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>10</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>3</v>
       </c>
     </row>
@@ -627,52 +656,55 @@
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
+        <v>248</v>
+      </c>
+      <c r="D10" s="2">
         <v>0.42768595041322316</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>0.4841</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>248</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>4</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>3</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>96</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>824</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>4</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34320</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <v>5</v>
       </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
       <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10">
         <v>1</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>8</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>3</v>
       </c>
     </row>
@@ -685,46 +717,49 @@
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
+        <v>249</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.4180327868852459</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>0.4668</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>249</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
       <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
         <v>98</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>827</v>
       </c>
-      <c r="O11">
-        <v>2</v>
-      </c>
       <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
         <v>6</v>
       </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
       <c r="R11">
         <v>2</v>
       </c>
       <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11">
         <v>5</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>3</v>
       </c>
     </row>
@@ -737,52 +772,55 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
+        <v>249</v>
+      </c>
+      <c r="D12" s="2">
         <v>0.4086242299794661</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>0.46595</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>249</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>1</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>102</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>830</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>1</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>148000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>1</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>3</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>4</v>
       </c>
-      <c r="R12">
-        <v>2</v>
-      </c>
       <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
         <v>4</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>3</v>
       </c>
     </row>
@@ -795,49 +833,52 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
+        <v>251</v>
+      </c>
+      <c r="D13" s="2">
         <v>0.42073170731707316</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>0.46715</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>251</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>6</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>6</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>108</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>1</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>148000</v>
       </c>
-      <c r="O13">
-        <v>2</v>
-      </c>
       <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
         <v>3</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>5</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>3</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>8</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>3</v>
       </c>
     </row>
